--- a/backend/data/financials_by_company/000767.SZ.xlsx
+++ b/backend/data/financials_by_company/000767.SZ.xlsx
@@ -4371,10 +4371,8 @@
           <t>Taiyuan</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>030006</t>
-        </is>
+      <c r="D2" t="n">
+        <v>30006</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -4597,7 +4595,7 @@
         <v>-116306200</v>
       </c>
       <c r="BQ2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
@@ -4846,7 +4844,7 @@
         <v>1650888000</v>
       </c>
       <c r="EH2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI2" t="n">
         <v>1.3509998</v>
